--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -28902,16 +28902,16 @@
         <v>46276.5625</v>
       </c>
       <c r="B1098" t="n">
-        <v>13493584</v>
+        <v>13571800</v>
       </c>
       <c r="C1098" t="n">
-        <v>6.40990018844604</v>
+        <v>6.40999984741211</v>
       </c>
       <c r="D1098" t="n">
         <v>6.25</v>
       </c>
       <c r="E1098" t="n">
-        <v>6.32999992370605</v>
+        <v>6.34000015258789</v>
       </c>
       <c r="F1098" t="n">
         <v>6.26000022888184</v>
@@ -28920,6 +28920,32 @@
         <v>6.26000022888184</v>
       </c>
       <c r="H1098" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>28471486</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>6.46999979019165</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>6.46999979019165</v>
+      </c>
+      <c r="H1099" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -28902,7 +28902,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1098" t="n">
-        <v>13571800</v>
+        <v>13676200</v>
       </c>
       <c r="C1098" t="n">
         <v>6.40999984741211</v>
@@ -28928,7 +28928,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1099" t="n">
-        <v>28471486</v>
+        <v>28606600</v>
       </c>
       <c r="C1099" t="n">
         <v>6.65000009536743</v>
@@ -28946,6 +28946,32 @@
         <v>6.46999979019165</v>
       </c>
       <c r="H1099" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>18497857</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>6.42000007629395</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>6.32999992370605</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1100" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -28954,7 +28954,7 @@
         <v>46280.5625</v>
       </c>
       <c r="B1100" t="n">
-        <v>18497857</v>
+        <v>18728200</v>
       </c>
       <c r="C1100" t="n">
         <v>6.42000007629395</v>
@@ -28972,6 +28972,32 @@
         <v>6.15000009536743</v>
       </c>
       <c r="H1100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1101" t="n">
+        <v>29477568</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>6.14499998092651</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>5.82999992370605</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>6.14499998092651</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="H1101" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -28980,7 +28980,7 @@
         <v>46281.5625</v>
       </c>
       <c r="B1101" t="n">
-        <v>29477568</v>
+        <v>29748500</v>
       </c>
       <c r="C1101" t="n">
         <v>6.14499998092651</v>
@@ -28998,6 +28998,32 @@
         <v>5.92999982833862</v>
       </c>
       <c r="H1101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1102" t="n">
+        <v>16580613</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>5.98999977111816</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1102" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29006,7 +29006,7 @@
         <v>46282.5625</v>
       </c>
       <c r="B1102" t="n">
-        <v>16580613</v>
+        <v>16688000</v>
       </c>
       <c r="C1102" t="n">
         <v>6.1100001335144</v>
@@ -29024,6 +29024,32 @@
         <v>6</v>
       </c>
       <c r="H1102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>19717799</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>6.07999992370605</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>5.82999992370605</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="H1103" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29032,7 +29032,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1103" t="n">
-        <v>19717799</v>
+        <v>19865600</v>
       </c>
       <c r="C1103" t="n">
         <v>6.07999992370605</v>
@@ -29041,7 +29041,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="E1103" t="n">
-        <v>6.05999994277954</v>
+        <v>6.05000019073486</v>
       </c>
       <c r="F1103" t="n">
         <v>5.92999982833862</v>
@@ -29050,6 +29050,32 @@
         <v>5.92999982833862</v>
       </c>
       <c r="H1103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>17705762</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>6.17000007629395</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>6.17000007629395</v>
+      </c>
+      <c r="H1104" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29032,7 +29032,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1103" t="n">
-        <v>19865600</v>
+        <v>19977800</v>
       </c>
       <c r="C1103" t="n">
         <v>6.07999992370605</v>
@@ -29058,7 +29058,7 @@
         <v>46286.5625</v>
       </c>
       <c r="B1104" t="n">
-        <v>17705762</v>
+        <v>17839200</v>
       </c>
       <c r="C1104" t="n">
         <v>6.21999979019165</v>
@@ -29067,7 +29067,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="E1104" t="n">
-        <v>6.09999990463257</v>
+        <v>6.09000015258789</v>
       </c>
       <c r="F1104" t="n">
         <v>6.17000007629395</v>
@@ -29076,6 +29076,32 @@
         <v>6.17000007629395</v>
       </c>
       <c r="H1104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1105" t="n">
+        <v>15182802</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>6.09000015258789</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>6.19000005722046</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>6.11999988555908</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>6.11999988555908</v>
+      </c>
+      <c r="H1105" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29084,7 +29084,7 @@
         <v>46287.5625</v>
       </c>
       <c r="B1105" t="n">
-        <v>15182802</v>
+        <v>15338300</v>
       </c>
       <c r="C1105" t="n">
         <v>6.21999979019165</v>
@@ -29102,6 +29102,32 @@
         <v>6.11999988555908</v>
       </c>
       <c r="H1105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="1" t="n">
+        <v>46288.5625</v>
+      </c>
+      <c r="B1106" t="n">
+        <v>11156051</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>6.14499998092651</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="H1106" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29110,7 +29110,7 @@
         <v>46288.5625</v>
       </c>
       <c r="B1106" t="n">
-        <v>11156051</v>
+        <v>11265700</v>
       </c>
       <c r="C1106" t="n">
         <v>6.15999984741211</v>
@@ -29119,7 +29119,7 @@
         <v>6</v>
       </c>
       <c r="E1106" t="n">
-        <v>6.14499998092651</v>
+        <v>6.13000011444092</v>
       </c>
       <c r="F1106" t="n">
         <v>6.01000022888184</v>
@@ -29128,6 +29128,32 @@
         <v>6.01000022888184</v>
       </c>
       <c r="H1106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>12323789</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>6.11999988555908</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>5.88000011444092</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>5.9899001121521</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1107" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29136,7 +29136,7 @@
         <v>46289.5625</v>
       </c>
       <c r="B1107" t="n">
-        <v>12323789</v>
+        <v>12369000</v>
       </c>
       <c r="C1107" t="n">
         <v>6.11999988555908</v>
@@ -29145,7 +29145,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="E1107" t="n">
-        <v>5.9899001121521</v>
+        <v>5.98999977111816</v>
       </c>
       <c r="F1107" t="n">
         <v>6.09999990463257</v>
@@ -29154,6 +29154,32 @@
         <v>6.09999990463257</v>
       </c>
       <c r="H1107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="1" t="n">
+        <v>46290.5625</v>
+      </c>
+      <c r="B1108" t="n">
+        <v>11786967</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>6.17000007629395</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>6.11999988555908</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="H1108" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29162,7 +29162,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1108" t="n">
-        <v>11786967</v>
+        <v>11847500</v>
       </c>
       <c r="C1108" t="n">
         <v>6.17000007629395</v>
@@ -29180,6 +29180,32 @@
         <v>6.05000019073486</v>
       </c>
       <c r="H1108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1109" t="n">
+        <v>14934531</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>6.03000020980835</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>5.82999992370605</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>5.82999992370605</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>5.82999992370605</v>
+      </c>
+      <c r="H1109" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29162,7 +29162,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1108" t="n">
-        <v>11847500</v>
+        <v>11873800</v>
       </c>
       <c r="C1108" t="n">
         <v>6.17000007629395</v>
@@ -29188,7 +29188,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1109" t="n">
-        <v>14934531</v>
+        <v>15055000</v>
       </c>
       <c r="C1109" t="n">
         <v>6.03000020980835</v>
@@ -29206,6 +29206,32 @@
         <v>5.82999992370605</v>
       </c>
       <c r="H1109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1110" t="n">
+        <v>14846280</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>6.00950002670288</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>5.81010007858276</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>5.90999984741211</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="H1110" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29214,16 +29214,16 @@
         <v>46294.5625</v>
       </c>
       <c r="B1110" t="n">
-        <v>14846280</v>
+        <v>14914500</v>
       </c>
       <c r="C1110" t="n">
-        <v>6.00950002670288</v>
+        <v>6.01000022888184</v>
       </c>
       <c r="D1110" t="n">
-        <v>5.81010007858276</v>
+        <v>5.80999994277954</v>
       </c>
       <c r="E1110" t="n">
-        <v>5.90999984741211</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="F1110" t="n">
         <v>5.84000015258789</v>
@@ -29232,6 +29232,32 @@
         <v>5.84000015258789</v>
       </c>
       <c r="H1110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1111" t="n">
+        <v>17247952</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>5.90229988098145</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="H1111" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29240,16 +29240,16 @@
         <v>46295.5625</v>
       </c>
       <c r="B1111" t="n">
-        <v>17247952</v>
+        <v>17346800</v>
       </c>
       <c r="C1111" t="n">
         <v>6.15000009536743</v>
       </c>
       <c r="D1111" t="n">
-        <v>5.90229988098145</v>
+        <v>5.90199995040894</v>
       </c>
       <c r="E1111" t="n">
-        <v>5.92999982833862</v>
+        <v>5.92000007629395</v>
       </c>
       <c r="F1111" t="n">
         <v>6.01999998092651</v>
@@ -29258,6 +29258,32 @@
         <v>6.01999998092651</v>
       </c>
       <c r="H1111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1112" t="n">
+        <v>13696750</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="H1112" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29266,7 +29266,7 @@
         <v>46296.5625</v>
       </c>
       <c r="B1112" t="n">
-        <v>13696750</v>
+        <v>13765900</v>
       </c>
       <c r="C1112" t="n">
         <v>6.17999982833862</v>
@@ -29284,6 +29284,32 @@
         <v>6.05000019073486</v>
       </c>
       <c r="H1112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1113" t="n">
+        <v>23429415</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>6.21000003814697</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>5.78000020980835</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="H1113" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29292,7 +29292,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1113" t="n">
-        <v>23429415</v>
+        <v>23540300</v>
       </c>
       <c r="C1113" t="n">
         <v>6.21000003814697</v>
@@ -29301,7 +29301,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="E1113" t="n">
-        <v>6.19999980926514</v>
+        <v>6.20499992370605</v>
       </c>
       <c r="F1113" t="n">
         <v>5.84000015258789</v>
@@ -29310,6 +29310,32 @@
         <v>5.84000015258789</v>
       </c>
       <c r="H1113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1114" t="n">
+        <v>13865900</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>5.88000011444092</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>5.88000011444092</v>
+      </c>
+      <c r="H1114" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29292,7 +29292,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1113" t="n">
-        <v>23540300</v>
+        <v>23682400</v>
       </c>
       <c r="C1113" t="n">
         <v>6.21000003814697</v>
@@ -29318,7 +29318,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1114" t="n">
-        <v>13865900</v>
+        <v>13997700</v>
       </c>
       <c r="C1114" t="n">
         <v>5.96999979019165</v>
@@ -29336,6 +29336,32 @@
         <v>5.88000011444092</v>
       </c>
       <c r="H1114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1115" t="n">
+        <v>18011319</v>
+      </c>
+      <c r="C1115" t="n">
+        <v>5.97499990463257</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="H1115" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29344,7 +29344,7 @@
         <v>46301.5625</v>
       </c>
       <c r="B1115" t="n">
-        <v>18011319</v>
+        <v>18246800</v>
       </c>
       <c r="C1115" t="n">
         <v>5.97499990463257</v>
@@ -29362,6 +29362,32 @@
         <v>5.71999979019165</v>
       </c>
       <c r="H1115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1116" t="n">
+        <v>14612912</v>
+      </c>
+      <c r="C1116" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="H1116" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29370,7 +29370,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1116" t="n">
-        <v>14612912</v>
+        <v>14781900</v>
       </c>
       <c r="C1116" t="n">
         <v>5.71000003814697</v>
@@ -29379,7 +29379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="E1116" t="n">
-        <v>5.65000009536743</v>
+        <v>5.6399998664856</v>
       </c>
       <c r="F1116" t="n">
         <v>5.63000011444092</v>
@@ -29388,6 +29388,32 @@
         <v>5.63000011444092</v>
       </c>
       <c r="H1116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1117" t="n">
+        <v>16881989</v>
+      </c>
+      <c r="C1117" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>5.44999980926514</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>5.56500005722046</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="H1117" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29396,7 +29396,7 @@
         <v>46303.5625</v>
       </c>
       <c r="B1117" t="n">
-        <v>16881989</v>
+        <v>16959600</v>
       </c>
       <c r="C1117" t="n">
         <v>5.59999990463257</v>
@@ -29405,7 +29405,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="E1117" t="n">
-        <v>5.56500005722046</v>
+        <v>5.57000017166138</v>
       </c>
       <c r="F1117" t="n">
         <v>5.51999998092651</v>
@@ -29414,6 +29414,32 @@
         <v>5.51999998092651</v>
       </c>
       <c r="H1117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1118" t="n">
+        <v>11819101</v>
+      </c>
+      <c r="C1118" t="n">
+        <v>5.61999988555908</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>5.3899998664856</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>5.3899998664856</v>
+      </c>
+      <c r="H1118" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29422,7 +29422,7 @@
         <v>46304.5625</v>
       </c>
       <c r="B1118" t="n">
-        <v>11819101</v>
+        <v>11886900</v>
       </c>
       <c r="C1118" t="n">
         <v>5.61999988555908</v>
@@ -29431,7 +29431,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="E1118" t="n">
-        <v>5.6100001335144</v>
+        <v>5.61999988555908</v>
       </c>
       <c r="F1118" t="n">
         <v>5.3899998664856</v>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29474,7 +29474,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1120" t="n">
-        <v>16604937</v>
+        <v>16706300</v>
       </c>
       <c r="C1120" t="n">
         <v>4.99499988555908</v>
@@ -29492,6 +29492,32 @@
         <v>4.88000011444092</v>
       </c>
       <c r="H1120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1121" t="n">
+        <v>19228222</v>
+      </c>
+      <c r="C1121" t="n">
+        <v>4.78000020980835</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>4.53000020980835</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>4.53000020980835</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>4.53000020980835</v>
+      </c>
+      <c r="H1121" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29500,7 +29500,7 @@
         <v>46309.5625</v>
       </c>
       <c r="B1121" t="n">
-        <v>19228222</v>
+        <v>19756400</v>
       </c>
       <c r="C1121" t="n">
         <v>4.78000020980835</v>
@@ -29518,6 +29518,32 @@
         <v>4.53000020980835</v>
       </c>
       <c r="H1121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1122" t="n">
+        <v>17922660</v>
+      </c>
+      <c r="C1122" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>4.38500022888184</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>4.8899998664856</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>4.8899998664856</v>
+      </c>
+      <c r="H1122" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -29526,7 +29526,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1122" t="n">
-        <v>17922660</v>
+        <v>18056600</v>
       </c>
       <c r="C1122" t="n">
         <v>4.90000009536743</v>
@@ -29544,6 +29544,32 @@
         <v>4.8899998664856</v>
       </c>
       <c r="H1122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1123" t="n">
+        <v>17828860</v>
+      </c>
+      <c r="C1123" t="n">
+        <v>4.92689990997314</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>4.8600001335144</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>4.71999979019165</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>4.71999979019165</v>
+      </c>
+      <c r="H1123" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -32939,7 +32939,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="H1123" t="n">
-        <v>17905800</v>
+        <v>17974400</v>
       </c>
       <c r="I1123" t="s">
         <v>9</v>
@@ -32968,9 +32968,38 @@
         <v>4.65000009536743</v>
       </c>
       <c r="H1124" t="n">
-        <v>12150427</v>
+        <v>12239900</v>
       </c>
       <c r="I1124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1125" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1125" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>10674959</v>
+      </c>
+      <c r="I1125" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -32997,9 +32997,38 @@
         <v>4.69999980926514</v>
       </c>
       <c r="H1125" t="n">
-        <v>10674959</v>
+        <v>10778700</v>
       </c>
       <c r="I1125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1126" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1126" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>4.82000017166138</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>4.6100001335144</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>4.6100001335144</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>11270621</v>
+      </c>
+      <c r="I1126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33011,7 +33011,7 @@
         <v>46316.5625</v>
       </c>
       <c r="C1126" t="n">
-        <v>4.80000019073486</v>
+        <v>4.79500007629395</v>
       </c>
       <c r="D1126" t="n">
         <v>4.82000017166138</v>
@@ -33026,9 +33026,38 @@
         <v>4.6100001335144</v>
       </c>
       <c r="H1126" t="n">
-        <v>11270621</v>
+        <v>11367500</v>
       </c>
       <c r="I1126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1127" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>4.67000007629395</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>10973728</v>
+      </c>
+      <c r="I1127" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33055,9 +33055,38 @@
         <v>4.5</v>
       </c>
       <c r="H1127" t="n">
-        <v>10973728</v>
+        <v>11038600</v>
       </c>
       <c r="I1127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1128" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="H1128" t="n">
+        <v>10623881</v>
+      </c>
+      <c r="I1128" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33084,9 +33084,38 @@
         <v>4.42999982833862</v>
       </c>
       <c r="H1128" t="n">
-        <v>10623881</v>
+        <v>10671600</v>
       </c>
       <c r="I1128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1129" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1129" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>13602627</v>
+      </c>
+      <c r="I1129" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33084,7 +33084,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="H1128" t="n">
-        <v>10671600</v>
+        <v>10722700</v>
       </c>
       <c r="I1128" t="s">
         <v>9</v>
@@ -33098,7 +33098,7 @@
         <v>46321.5625</v>
       </c>
       <c r="C1129" t="n">
-        <v>4.38000011444092</v>
+        <v>4.375</v>
       </c>
       <c r="D1129" t="n">
         <v>4.40999984741211</v>
@@ -33113,9 +33113,38 @@
         <v>4.23999977111816</v>
       </c>
       <c r="H1129" t="n">
-        <v>13602627</v>
+        <v>13717100</v>
       </c>
       <c r="I1129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1130" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>4.49709987640381</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>17972399</v>
+      </c>
+      <c r="I1130" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33127,10 +33127,10 @@
         <v>46322.5625</v>
       </c>
       <c r="C1130" t="n">
-        <v>4.30000019073486</v>
+        <v>4.28999996185303</v>
       </c>
       <c r="D1130" t="n">
-        <v>4.49709987640381</v>
+        <v>4.49700021743774</v>
       </c>
       <c r="E1130" t="n">
         <v>4.28000020980835</v>
@@ -33142,9 +33142,38 @@
         <v>4.36999988555908</v>
       </c>
       <c r="H1130" t="n">
-        <v>17972399</v>
+        <v>18066200</v>
       </c>
       <c r="I1130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1131" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>12845111</v>
+      </c>
+      <c r="I1131" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33156,10 +33156,10 @@
         <v>46323.5625</v>
       </c>
       <c r="C1131" t="n">
-        <v>4.38000011444092</v>
+        <v>4.36999988555908</v>
       </c>
       <c r="D1131" t="n">
-        <v>4.44999980926514</v>
+        <v>4.45499992370605</v>
       </c>
       <c r="E1131" t="n">
         <v>4.26000022888184</v>
@@ -33171,9 +33171,38 @@
         <v>4.44000005722046</v>
       </c>
       <c r="H1131" t="n">
-        <v>12845111</v>
+        <v>12958400</v>
       </c>
       <c r="I1131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1132" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>4.35500001907349</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>4.29099988937378</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>10762654</v>
+      </c>
+      <c r="I1132" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOUN.xlsx
+++ b/data/SOUN.xlsx
@@ -33191,7 +33191,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="E1132" t="n">
-        <v>4.29099988937378</v>
+        <v>4.28999996185303</v>
       </c>
       <c r="F1132" t="n">
         <v>4.3600001335144</v>
@@ -33200,9 +33200,38 @@
         <v>4.3600001335144</v>
       </c>
       <c r="H1132" t="n">
-        <v>10762654</v>
+        <v>10980000</v>
       </c>
       <c r="I1132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1133" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>4.21500015258789</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>16120398</v>
+      </c>
+      <c r="I1133" t="s">
         <v>9</v>
       </c>
     </row>
